--- a/src/index_travel_accessibility/data/processed/nearest_hospitals_to_sample_points.xlsx
+++ b/src/index_travel_accessibility/data/processed/nearest_hospitals_to_sample_points.xlsx
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.2370854</v>
+        <v>49.2371047</v>
       </c>
       <c r="F4" t="n">
-        <v>6.9925905</v>
+        <v>6.9925617</v>
       </c>
       <c r="G4" t="n">
-        <v>0.892</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="5">

--- a/src/index_travel_accessibility/data/processed/nearest_hospitals_to_sample_points.xlsx
+++ b/src/index_travel_accessibility/data/processed/nearest_hospitals_to_sample_points.xlsx
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.2371047</v>
+        <v>49.2370854</v>
       </c>
       <c r="F4" t="n">
-        <v>6.9925617</v>
+        <v>6.9925905</v>
       </c>
       <c r="G4" t="n">
-        <v>0.89</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="5">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.4571859</v>
+        <v>49.4590255</v>
       </c>
       <c r="F9" t="n">
-        <v>6.6315777</v>
+        <v>6.6299114</v>
       </c>
       <c r="G9" t="n">
-        <v>4.445</v>
+        <v>4.322</v>
       </c>
     </row>
     <row r="10">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49.4571859</v>
+        <v>49.4590255</v>
       </c>
       <c r="F10" t="n">
-        <v>6.6315777</v>
+        <v>6.6299114</v>
       </c>
       <c r="G10" t="n">
-        <v>10.122</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="11">
